--- a/resampling/input/accessibility_reports_returned/CARE_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/CARE_accessibility_report.xlsx
@@ -246,8 +246,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:M224" headerRowCount="1">
-  <autoFilter ref="A1:M224"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:M256" headerRowCount="1">
+  <autoFilter ref="A1:M256"/>
   <tableColumns count="13">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -8536,7 +8536,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr"/>
       <c r="G212" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -8614,7 +8613,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -8651,7 +8649,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr"/>
       <c r="G215" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -8688,7 +8685,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -8807,7 +8803,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -9008,7 +9003,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -9045,7 +9039,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr"/>
       <c r="G225" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -9082,7 +9075,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -9119,7 +9111,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -9156,7 +9147,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -9193,7 +9183,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -9230,7 +9219,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -9308,7 +9296,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -9345,7 +9332,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -9382,7 +9368,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -9419,7 +9404,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -9538,7 +9522,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -9657,7 +9640,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -9735,7 +9717,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -9936,7 +9917,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr"/>
       <c r="G248" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -9973,7 +9953,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr"/>
       <c r="G249" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -10256,7 +10235,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -10416,7 +10394,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F260" t="inlineStr"/>
       <c r="G260" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -10494,7 +10471,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -10531,7 +10507,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr"/>
       <c r="G263" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -10568,7 +10543,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr"/>
       <c r="G264" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -10728,7 +10702,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F268" t="inlineStr"/>
       <c r="G268" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -10765,7 +10738,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F269" t="inlineStr"/>
       <c r="G269" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -11335,7 +11307,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F283" t="inlineStr"/>
       <c r="G283" t="inlineStr">
         <is>
           <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
@@ -11787,7 +11758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M224"/>
+  <dimension ref="A1:M256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" style="12" min="1" max="2"/>
@@ -20376,12 +20347,1276 @@
         </is>
       </c>
     </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Nasarawa</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Obi</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Duduguru</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>non_idp_NG026011_supp3</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Ngala</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Ngala</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>non_idp_NG008025_supp11</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Charanchi</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Tsakatsa</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>non_idp_NG021006_supp1</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Ngala</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Ngala</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>non_idp_NG008025_supp12</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Ngala</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Ngala</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>non_idp_NG008025_supp13</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Ngala</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Ngala</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>non_idp_NG008025_supp14</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Ngala</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Ngala</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>non_idp_NG008025_supp15</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Ngala</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Ngala</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>non_idp_NG008025_supp16</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Nasarawa</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Akwanga</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Wasa</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>non_idp_NG026001_supp1</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Nasarawa</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Akwanga</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Alushi-Ginda / Aloce</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>non_idp_NG026001_supp2</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Nasarawa</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Akwanga</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Agyaga</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>non_idp_NG026001_supp3</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Nasarawa</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Akwanga</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Agyaga</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>non_idp_NG026001_supp4</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Nasarawa</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Lafia</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Shabu Kwandare</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>non_idp_NG026008_supp1</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Argungu</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Lailaba</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>non_idp_NG022003_supp1</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Argungu</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Sauwa</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>non_idp_NG022003_supp2</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Birnin Kebbi</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Kardi</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>non_idp_NG022006_supp1</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Birnin Kebbi</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Kardi</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>non_idp_NG022006_supp2</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Birnin Kebbi</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Maurida</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>non_idp_NG022006_supp3</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Birnin Kebbi</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Kardi</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>non_idp_NG022006_supp4</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Ngala</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Gamboru C</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>non_idp_NG008025_supp17</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Ngala</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Ngala</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>idp_NG008025_supp1</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Charanchi</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Kuraye</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>idp_NG021006_supp1</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Charanchi</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Charanchi</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>idp_NG021006_supp2</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Charanchi</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Charanchi</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>idp_NG021006_supp3</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Charanchi</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Charanchi</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>idp_NG021006_supp4</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Charanchi</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Charanchi</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>idp_NG021006_supp5</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Nasarawa</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Awe</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Jangaru</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>idp_NG026002_supp1</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Nasarawa</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Kokona</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Garaku</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>idp_NG026007_supp1</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Nasarawa</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Nasarawa-Eggon</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Kagbu</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>idp_NG026010_supp1</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Nasarawa</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Nasarawa-Eggon</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Kagbu</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>idp_NG026010_supp2</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Nasarawa</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Nasarawa-Eggon</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Ende</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>idp_NG026010_supp3</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Nasarawa</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Nasarawa-Eggon</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Nassarawa-Eggon</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>idp_NG026010_supp4</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="I2:I224" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I256" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J224" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J256" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
   </dataValidations>
@@ -20648,13 +21883,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A307CA50-131D-44A4-B5CE-79DCBB468183}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69920729-217E-49C7-94C7-C5F7EE9B46DA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{838F39F3-8B77-4D3D-A8E2-2819D328F7A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26DDAF3C-1AC7-459E-8DDB-2A7BEE0626E9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCA39DA7-7E52-456F-811C-8E2BD06076EB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFED4503-2BC6-47BB-B37C-9E53FA8124F3}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/CARE_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/CARE_accessibility_report.xlsx
@@ -246,8 +246,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:M256" headerRowCount="1">
-  <autoFilter ref="A1:M256"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:M257" headerRowCount="1">
+  <autoFilter ref="A1:M257"/>
   <tableColumns count="13">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -11758,7 +11758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M256"/>
+  <dimension ref="A1:M257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" style="12" min="1" max="2"/>
@@ -20373,7 +20373,6 @@
           <t>non_idp_NG026011_supp3</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr"/>
       <c r="G225" t="inlineStr">
         <is>
           <t>6</t>
@@ -20411,7 +20410,6 @@
           <t>non_idp_NG008025_supp11</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr">
         <is>
           <t>6</t>
@@ -20449,7 +20447,6 @@
           <t>non_idp_NG021006_supp1</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr">
         <is>
           <t>6</t>
@@ -20487,7 +20484,6 @@
           <t>non_idp_NG008025_supp12</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr">
         <is>
           <t>6</t>
@@ -20525,7 +20521,6 @@
           <t>non_idp_NG008025_supp13</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr">
         <is>
           <t>6</t>
@@ -20563,7 +20558,6 @@
           <t>non_idp_NG008025_supp14</t>
         </is>
       </c>
-      <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr">
         <is>
           <t>6</t>
@@ -20601,7 +20595,6 @@
           <t>non_idp_NG008025_supp15</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr"/>
       <c r="G231" t="inlineStr">
         <is>
           <t>6</t>
@@ -20639,7 +20632,6 @@
           <t>non_idp_NG008025_supp16</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr">
         <is>
           <t>6</t>
@@ -20677,7 +20669,6 @@
           <t>non_idp_NG026001_supp1</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr">
         <is>
           <t>6</t>
@@ -20715,7 +20706,6 @@
           <t>non_idp_NG026001_supp2</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr">
         <is>
           <t>6</t>
@@ -20753,7 +20743,6 @@
           <t>non_idp_NG026001_supp3</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr">
         <is>
           <t>6</t>
@@ -20791,7 +20780,6 @@
           <t>non_idp_NG026001_supp4</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr">
         <is>
           <t>6</t>
@@ -20829,7 +20817,6 @@
           <t>non_idp_NG026008_supp1</t>
         </is>
       </c>
-      <c r="F237" t="inlineStr"/>
       <c r="G237" t="inlineStr">
         <is>
           <t>6</t>
@@ -20867,7 +20854,6 @@
           <t>non_idp_NG022003_supp1</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr">
         <is>
           <t>6</t>
@@ -20905,7 +20891,6 @@
           <t>non_idp_NG022003_supp2</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr">
         <is>
           <t>6</t>
@@ -20943,7 +20928,6 @@
           <t>non_idp_NG022006_supp1</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr">
         <is>
           <t>6</t>
@@ -20981,7 +20965,6 @@
           <t>non_idp_NG022006_supp2</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr">
         <is>
           <t>6</t>
@@ -21019,7 +21002,6 @@
           <t>non_idp_NG022006_supp3</t>
         </is>
       </c>
-      <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr">
         <is>
           <t>6</t>
@@ -21057,7 +21039,6 @@
           <t>non_idp_NG022006_supp4</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr">
         <is>
           <t>6</t>
@@ -21095,7 +21076,6 @@
           <t>non_idp_NG008025_supp17</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr">
         <is>
           <t>6</t>
@@ -21611,12 +21591,50 @@
         </is>
       </c>
     </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Ngala</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Ngala</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>non_idp_NG008025_supp18</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="I2:I256" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I257" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J256" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J257" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
   </dataValidations>
@@ -21625,271 +21643,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
-    <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
-    <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="30973102-2308-455b-8e1f-b6a90edc3b23" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{daf5bdda-bc47-491d-9935-b3e42d5c0ae4}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="947c1918-d5ab-48a1-8b61-0d52f2f99fd1">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="30973102-2308-455b-8e1f-b6a90edc3b23">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69920729-217E-49C7-94C7-C5F7EE9B46DA}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26DDAF3C-1AC7-459E-8DDB-2A7BEE0626E9}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFED4503-2BC6-47BB-B37C-9E53FA8124F3}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/CARE_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/CARE_accessibility_report.xlsx
@@ -21643,4 +21643,271 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
+    <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
+    <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="30973102-2308-455b-8e1f-b6a90edc3b23" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{daf5bdda-bc47-491d-9935-b3e42d5c0ae4}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="947c1918-d5ab-48a1-8b61-0d52f2f99fd1">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="30973102-2308-455b-8e1f-b6a90edc3b23">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7853FFA0-BC20-4640-9320-3AE132431F06}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE55FA65-4EBF-430E-BEEA-BDB529D250BE}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F878F32-C992-4E77-8402-4A735FC90A5D}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/CARE_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/CARE_accessibility_report.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acted.sharepoint.com/sites/IMPACTNGA/Documents partages/General/01. NGA IMPACT Mission Files/2025-2026/04 ECHO HIP 2026/02. MSNA/4. Data/MSNA N-WEC 2026/1_sampling/resampling/input/accessibility_reports_returned/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acted.sharepoint.com/sites/IMPACTNGA/Documents partages/General/01. NGA IMPACT Mission Files/2025-2026/04 ECHO HIP 2026/02. MSNA/4. Data/MSNA N-WEC 2026/1_sampling/resampling/input/partner_raw_comms/CARE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_74694E132F2F17DC3E5D0890056C53250CD1EF0B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABE5FBAB-D610-4964-AD12-E82DB91C220F}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{A269097D-A1D2-4A12-B76D-585373B1B16B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82D2B3BA-0F94-44EA-B6C1-3ABD4AE45763}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="5130" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,12 +17,25 @@
     <sheet name="Ward Accessibility" sheetId="2" r:id="rId2"/>
     <sheet name="Cluster Accessibility" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3438" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3441" uniqueCount="606">
   <si>
     <t>State</t>
   </si>
@@ -1837,6 +1850,9 @@
   </si>
   <si>
     <t>Awe; Lafia</t>
+  </si>
+  <si>
+    <t>Physical access (terrain</t>
   </si>
 </sst>
 </file>
@@ -1975,7 +1991,7 @@
   <autoFilter ref="A1:O293" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Charanchi"/>
+        <filter val="Ngala"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2446,12 +2462,12 @@
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="28.26953125" customWidth="1"/>
-    <col min="4" max="4" width="19" hidden="1" customWidth="1"/>
-    <col min="5" max="6" width="30" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="14" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="20" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="16" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="30" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
     <col min="11" max="11" width="20" customWidth="1"/>
     <col min="12" max="12" width="19" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
@@ -2506,7 +2522,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -2532,7 +2548,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -2567,7 +2583,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -2602,7 +2618,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -2637,7 +2653,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -2672,7 +2688,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -2704,7 +2720,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -2745,7 +2761,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -2780,7 +2796,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>49</v>
       </c>
@@ -2803,7 +2819,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>49</v>
       </c>
@@ -2826,7 +2842,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>49</v>
       </c>
@@ -2855,7 +2871,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -2883,8 +2899,14 @@
       <c r="J13">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="K13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L13" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>49</v>
       </c>
@@ -2913,7 +2935,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>49</v>
       </c>
@@ -2941,8 +2963,11 @@
       <c r="J15">
         <v>12</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="K15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -2971,7 +2996,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -2994,7 +3019,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>49</v>
       </c>
@@ -3023,7 +3048,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -3052,7 +3077,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -5975,7 +6000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>13</v>
       </c>
@@ -6002,7 +6027,7 @@
       </c>
       <c r="O139" s="11"/>
     </row>
-    <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>13</v>
       </c>
@@ -6518,7 +6543,7 @@
       </c>
       <c r="O158" s="11"/>
     </row>
-    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>13</v>
       </c>
@@ -6547,7 +6572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>13</v>
       </c>
@@ -6576,7 +6601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>13</v>
       </c>
@@ -6605,7 +6630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>13</v>
       </c>
@@ -6634,7 +6659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>49</v>
       </c>
@@ -6663,7 +6688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>49</v>
       </c>
@@ -6692,7 +6717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>49</v>
       </c>
@@ -6721,7 +6746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>49</v>
       </c>
@@ -6750,7 +6775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>49</v>
       </c>
@@ -6779,7 +6804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>49</v>
       </c>
@@ -6808,7 +6833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>49</v>
       </c>
@@ -6837,7 +6862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>49</v>
       </c>
@@ -6866,7 +6891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>49</v>
       </c>
@@ -6895,7 +6920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>49</v>
       </c>
@@ -6924,7 +6949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>49</v>
       </c>
@@ -6953,7 +6978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>49</v>
       </c>
@@ -16519,8 +16544,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="7a2915931200ea69f6d4702d545d15c4">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ebf5164e0bbea30cbcbeb97056918f83" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
     <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
     <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
     <xsd:element name="properties">
@@ -16568,7 +16593,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Balises d’images" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -16627,7 +16652,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Partagé avec" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -16646,7 +16671,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Partagé avec détails" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -16663,8 +16688,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Type de contenu"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titre"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -16774,7 +16799,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C238E699-E557-447F-9F74-B82DB1323242}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDF2C317-D0C0-47AB-AF4C-39E2F875F632}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
